--- a/database/seeders/excel/room.xlsx
+++ b/database/seeders/excel/room.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\mlti\database\seeders\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8517B7CB-7BB9-462A-B0C7-E8BCAD40F905}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0D6537-F44D-48F5-96DB-63C8D176A3DB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Ruang Aula</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>Ruang Humas</t>
+  </si>
+  <si>
+    <t>BPS Kabupaten Kota</t>
   </si>
 </sst>
 </file>
@@ -402,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -555,9 +558,17 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
+        <v>98</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>99</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>16</v>
       </c>
     </row>
